--- a/OMOP Analysis/Results/Output_costs_OMOP-Adjusted.xlsx
+++ b/OMOP Analysis/Results/Output_costs_OMOP-Adjusted.xlsx
@@ -414,7 +414,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1016.32</v>
+        <v>1192.27</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -423,28 +423,28 @@
         <v>14096</v>
       </c>
       <c r="D2">
-        <v>983.22</v>
+        <v>1010.86</v>
       </c>
       <c r="E2">
-        <v>756</v>
+        <v>932.63</v>
       </c>
       <c r="F2">
-        <v>336</v>
+        <v>511.38</v>
       </c>
       <c r="G2">
-        <v>1381.85</v>
+        <v>1565.95</v>
       </c>
       <c r="H2">
-        <v>13178</v>
+        <v>14956</v>
       </c>
       <c r="I2">
-        <v>8.564972097615595</v>
+        <v>8.265769369732171</v>
       </c>
       <c r="J2">
-        <v>999.5314210585706</v>
+        <v>1176.068078449835</v>
       </c>
       <c r="K2">
-        <v>1033.108578941429</v>
+        <v>1208.471921550165</v>
       </c>
     </row>
   </sheetData>
@@ -516,37 +516,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1049.53</v>
+        <v>1204.67</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C2">
         <v>14096</v>
       </c>
       <c r="D2">
-        <v>981.5599999999999</v>
+        <v>1008.73</v>
       </c>
       <c r="E2">
-        <v>787.1799999999999</v>
+        <v>943.29</v>
       </c>
       <c r="F2">
-        <v>378</v>
+        <v>529.2</v>
       </c>
       <c r="G2">
-        <v>1409.32</v>
+        <v>1576.69</v>
       </c>
       <c r="H2">
-        <v>12761</v>
+        <v>14802</v>
       </c>
       <c r="I2">
-        <v>8.689094041956455</v>
+        <v>8.291149329358959</v>
       </c>
       <c r="J2">
-        <v>1032.498073038765</v>
+        <v>1188.418316930282</v>
       </c>
       <c r="K2">
-        <v>1066.561926961235</v>
+        <v>1220.921683069718</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_costs_OMOP-Adjusted.xlsx
+++ b/OMOP Analysis/Results/Output_costs_OMOP-Adjusted.xlsx
@@ -414,37 +414,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1192.27</v>
+        <v>603581.21</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>14096</v>
+        <v>222081427.76</v>
       </c>
       <c r="D2">
-        <v>1010.86</v>
+        <v>2609254.93</v>
       </c>
       <c r="E2">
-        <v>932.63</v>
+        <v>185258.61</v>
       </c>
       <c r="F2">
-        <v>511.38</v>
+        <v>55899.9</v>
       </c>
       <c r="G2">
-        <v>1565.95</v>
+        <v>529453.97</v>
       </c>
       <c r="H2">
         <v>14956</v>
       </c>
       <c r="I2">
-        <v>8.265769369732171</v>
+        <v>21335.79276874806</v>
       </c>
       <c r="J2">
-        <v>1176.068078449835</v>
+        <v>561760.4398832272</v>
       </c>
       <c r="K2">
-        <v>1208.471921550165</v>
+        <v>645401.9801167727</v>
       </c>
     </row>
   </sheetData>
@@ -516,37 +516,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1204.67</v>
+        <v>4633.2</v>
       </c>
       <c r="B2">
-        <v>12</v>
+        <v>1.65</v>
       </c>
       <c r="C2">
-        <v>14096</v>
+        <v>76184</v>
       </c>
       <c r="D2">
-        <v>1008.73</v>
+        <v>4383.34</v>
       </c>
       <c r="E2">
-        <v>943.29</v>
+        <v>3484.06</v>
       </c>
       <c r="F2">
-        <v>529.2</v>
+        <v>1784.99</v>
       </c>
       <c r="G2">
-        <v>1576.69</v>
+        <v>6089.24</v>
       </c>
       <c r="H2">
-        <v>14802</v>
+        <v>14808</v>
       </c>
       <c r="I2">
-        <v>8.291149329358959</v>
+        <v>36.02109873390648</v>
       </c>
       <c r="J2">
-        <v>1188.418316930282</v>
+        <v>4562.594172292414</v>
       </c>
       <c r="K2">
-        <v>1220.921683069718</v>
+        <v>4703.805827707586</v>
       </c>
     </row>
   </sheetData>
